--- a/out/LSTM-mamba2_repeat_5_000001.xlsx
+++ b/out/LSTM-mamba2_repeat_5_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.9409673395990859</v>
+        <v>2.90780289896909</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.9409673395990859</v>
+        <v>2.90780289896909</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.540967339599086</v>
+        <v>3.50780289896909</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.279412977671564</v>
+        <v>3.50780289896909</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.879412977671564</v>
+        <v>3.50780289896909</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.879412977671564</v>
+        <v>3.50780289896909</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.879412977671564</v>
+        <v>3.50780289896909</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.879412977671564</v>
+        <v>3.50780289896909</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.879412977671564</v>
+        <v>3.50780289896909</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.879412977671564</v>
+        <v>2.90780289896909</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.879412977671564</v>
+        <v>2.90780289896909</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.879412977671564</v>
+        <v>2.90780289896909</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.879412977671564</v>
+        <v>2.90780289896909</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.879412977671564</v>
+        <v>2.90780289896909</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.879412977671564</v>
+        <v>2.90780289896909</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.879412977671564</v>
+        <v>3.50780289896909</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.879412977671564</v>
+        <v>3.50780289896909</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.879412977671564</v>
+        <v>3.50780289896909</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.879412977671564</v>
+        <v>3.50780289896909</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.879412977671564</v>
+        <v>3.50780289896909</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.3110100759941125</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.540967339599086</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.540967339599086</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002258591469477396</v>
+        <v>-2.559288044471759e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.09724839110096826</v>
+        <v>0.0110195512580212</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.540967339599086</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.1947563124461484</v>
+        <v>0.02206851078487572</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3757219649518096</v>
+        <v>0.04257352685804452</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.279412977671564</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.849200540282916</v>
+        <v>0.09622584942793054</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1155741826082087</v>
+        <v>0.01309585551645406</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.279412977671564</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.70415130824545</v>
+        <v>0.07978950142283109</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02345086136694857</v>
+        <v>0.002654006027363967</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.6352980435920551</v>
+        <v>0.07198380541414232</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02030948816776322</v>
+        <v>0.002297465567753026</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.6524402333179438</v>
+        <v>0.07392268332647463</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.009928847834295072</v>
+        <v>0.001120628506137802</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.540967339599086</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.6519622434146511</v>
+        <v>0.07386408406024636</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.004735677580805586</v>
+        <v>0.0005322099753301889</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.540967339599086</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.6514948369126301</v>
+        <v>0.07380665623611049</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001970207800388299</v>
+        <v>0.0002187975016223495</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.540967339599086</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.650693463284564</v>
+        <v>0.07371131290502636</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.00136394522330634</v>
+        <v>0.0001501059694952505</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.540967339599086</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.6514493574801991</v>
+        <v>0.07379273992464598</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0005664825899902985</v>
+        <v>6.007298939010162e-05</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.540967339599086</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.6512168893012729</v>
+        <v>0.07376183881295309</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002910000237204896</v>
+        <v>2.840858055536001e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.540967339599086</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.6512324800402725</v>
+        <v>0.07375918403839413</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001115198271919516</v>
+        <v>8.121602161255812e-06</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.540967339599086</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.6511635024044903</v>
+        <v>0.07374683586997959</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>5.856229200828367e-05</v>
+        <v>2.444232397366555e-06</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.540967339599086</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.6511689772073888</v>
+        <v>0.07374306264869752</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>2.605694527035538e-05</v>
+        <v>-1.611969606870321e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.6511630222373039</v>
+        <v>0.07373795136862225</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>9.919117236739567e-06</v>
+        <v>-3.401523153206475e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.6511562020561725</v>
+        <v>0.0737327244648377</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.456405945771008e-06</v>
+        <v>-4.077656293461284e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.6511491772176118</v>
+        <v>0.073727435202186</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-2.106181251314092e-06</v>
+        <v>-4.586597321616299e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.651143499986042</v>
+        <v>0.07372233845481882</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-4.04640701416283e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.6511378274757578</v>
+        <v>0.07372224280168535</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.634963333793937e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.6511322838076553</v>
+        <v>0.07372210729307961</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.777674021158921e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.6511273626539339</v>
+        <v>0.07372214714855188</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.6511274025094063</v>
+        <v>0.07372218700402416</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.6511273945383117</v>
+        <v>0.07372217903292971</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.6511275539602008</v>
+        <v>0.07372233845481882</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.6511274583070674</v>
+        <v>0.07372224280168535</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.6511278090352237</v>
+        <v>0.07372259352984163</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.6511275619312953</v>
+        <v>0.07372234642591327</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.651127522075823</v>
+        <v>0.073722306570441</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.6511274583070674</v>
+        <v>0.07372224280168535</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.6511275300469175</v>
+        <v>0.07372231454153545</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.6511274583070674</v>
+        <v>0.07372224280168535</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.6511275619312953</v>
+        <v>0.07372234642591327</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.651127657584429</v>
+        <v>0.07372244207904698</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.6511275938156731</v>
+        <v>0.0737223783102911</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.6511275539602008</v>
+        <v>0.07372233845481882</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.6511275300469175</v>
+        <v>0.07372231454153545</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.540967339599086</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.6511272829429894</v>
+        <v>0.07372206743760733</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.540967339599086</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.6511272032320445</v>
+        <v>0.07372198772666254</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.540967339599086</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.6511272510586114</v>
+        <v>0.07372203555322927</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.540967339599086</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.6511273706250283</v>
+        <v>0.07372215511964635</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.540967339599086</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.6511273546828394</v>
+        <v>0.07372213917745743</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.540967339599086</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.6511273706250283</v>
+        <v>0.07372215511964635</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.540967339599086</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.6511273546828394</v>
+        <v>0.07372213917745743</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.6511274104805007</v>
+        <v>0.07372219497511862</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.6511274104805007</v>
+        <v>0.07372219497511862</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.6511274104805007</v>
+        <v>0.07372219497511862</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.6511275619312953</v>
+        <v>0.07372234642591327</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.540967339599086</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.6511277771508458</v>
+        <v>0.07372256164546381</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.6511276894688068</v>
+        <v>0.07372247396342479</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.6511276416422401</v>
+        <v>0.07372242613685806</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.6511276894688068</v>
+        <v>0.07372247396342479</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.540967339599086</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.6511275061336341</v>
+        <v>0.07372229062825209</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.540967339599086</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.6511275141047286</v>
+        <v>0.07372229859934654</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.540967339599086</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.651127522075823</v>
+        <v>0.073722306570441</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.540967339599086</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.6511275300469175</v>
+        <v>0.07372231454153545</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.540967339599086</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.6511275300469175</v>
+        <v>0.07372231454153545</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.540967339599086</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.6511275699023897</v>
+        <v>0.07372235439700774</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.540967339599086</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.6511276336711457</v>
+        <v>0.07372241816576361</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.651127745266468</v>
+        <v>0.07372252976108598</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.6511277930930348</v>
+        <v>0.07372257758765272</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.6511277532375624</v>
+        <v>0.07372253773218045</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.6511276814977124</v>
+        <v>0.07372246599233034</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.6511278010641293</v>
+        <v>0.07372258555874718</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.6511276416422401</v>
+        <v>0.07372242613685806</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.6511274104805007</v>
+        <v>0.07372219497511862</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.6511273626539339</v>
+        <v>0.07372214714855188</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.6511273945383117</v>
+        <v>0.07372217903292971</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.6511274583070674</v>
+        <v>0.07372224280168535</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.6511274583070674</v>
+        <v>0.07372224280168535</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.6511273785961228</v>
+        <v>0.0737221630907408</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.6511272590297058</v>
+        <v>0.07372204352432372</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.6511272191742336</v>
+        <v>0.07372200366885145</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.9409673395990859</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.6511273626539339</v>
+        <v>0.07372214714855188</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.6511274981625397</v>
+        <v>0.07372228265715763</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.6511274822203508</v>
+        <v>0.07372226671496872</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.6511274583070674</v>
+        <v>0.07372224280168535</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.6511274184515952</v>
+        <v>0.07372220294621308</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.6511273148273672</v>
+        <v>0.07372209932198515</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.540967339599086</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.6511271952609501</v>
+        <v>0.07372197975556809</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.279412977671564</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.6511273148273672</v>
+        <v>0.07372209932198515</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.279412977671564</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.6511273626539339</v>
+        <v>0.07372214714855188</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.6511274583070674</v>
+        <v>0.07372224280168535</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.6511273387406505</v>
+        <v>0.07372212323526851</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.540967339599086</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.651127346711745</v>
+        <v>0.07372213120636298</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-mamba2_repeat_5_000001.xlsx
+++ b/out/LSTM-mamba2_repeat_5_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.9409673395990859</v>
+        <v>0.8109490328679446</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.9409673395990859</v>
+        <v>0.8109490328679446</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.540967339599086</v>
+        <v>0.3662906746346532</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.279412977671564</v>
+        <v>-0.2783676835986383</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.2783676835986383</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.540967339599086</v>
+        <v>0.3662906746346533</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.540967339599086</v>
+        <v>1.010949032867945</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002258591469477396</v>
+        <v>-0.0001825695434312802</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.09724839110096826</v>
+        <v>0.07860914469337262</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.540967339599086</v>
+        <v>0.3662906746346532</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.1947563124461484</v>
+        <v>0.1574280764103516</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3757219649518096</v>
+        <v>0.3037086986530208</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.279412977671564</v>
+        <v>-0.2783676835986383</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.849200540282916</v>
+        <v>0.6864373527319496</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1155741826082087</v>
+        <v>0.09342198919729137</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.279412977671564</v>
+        <v>-0.9230260418319297</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.70415130824545</v>
+        <v>0.5691891820515259</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02345086136694857</v>
+        <v>0.01895601654148876</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.4783676835986383</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.6352980435920551</v>
+        <v>0.5135324703474878</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02030948816776322</v>
+        <v>0.0164167527850336</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.9409673395990859</v>
+        <v>0.1662906746346532</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.6524402333179438</v>
+        <v>0.5273893061463832</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.009928847834295072</v>
+        <v>0.00802490335441961</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.540967339599086</v>
+        <v>1.010949032867945</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.6519622434146511</v>
+        <v>0.5270020424989373</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.004735677580805586</v>
+        <v>0.0038276323613109</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.540967339599086</v>
+        <v>1.010949032867945</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.6514948369126301</v>
+        <v>0.5266232326600649</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001970207800388299</v>
+        <v>0.001591644862320643</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.540967339599086</v>
+        <v>1.010949032867945</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.650693463284564</v>
+        <v>0.5259744898288097</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.00136394522330634</v>
+        <v>0.001101576916697459</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.540967339599086</v>
+        <v>1.010949032867945</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.6514493574801991</v>
+        <v>0.5265845531188552</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0005664825899902985</v>
+        <v>0.0004569537959673552</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.540967339599086</v>
+        <v>1.010949032867945</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.6512168893012729</v>
+        <v>0.5263956808705008</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002910000237204896</v>
+        <v>0.0002342054367763777</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.540967339599086</v>
+        <v>1.010949032867945</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.6512324800402725</v>
+        <v>0.5264073253788326</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001115198271919516</v>
+        <v>8.895067147459162e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.540967339599086</v>
+        <v>1.010949032867945</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.6511635024044903</v>
+        <v>0.5263505963279386</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>5.856229200828367e-05</v>
+        <v>4.653699352023e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.540967339599086</v>
+        <v>1.010949032867945</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.6511689772073888</v>
+        <v>0.5263540894113697</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>2.605694527035538e-05</v>
+        <v>2.041022794847258e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.9409673395990859</v>
+        <v>1.010949032867945</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.6511630222373039</v>
+        <v>0.5263483145940139</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>9.919117236739567e-06</v>
+        <v>6.722163543152517e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.9409673395990859</v>
+        <v>0.8109490328679446</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.6511562020561725</v>
+        <v>0.5263418525673186</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.456405945771008e-06</v>
+        <v>7.289038596293463e-08</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.9409673395990859</v>
+        <v>0.8109490328679446</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.6511491772176118</v>
+        <v>0.526335189882885</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-2.106181251314092e-06</v>
+        <v>-2.519583929697793e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.9409673395990859</v>
+        <v>0.8109490328679446</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.651143499986042</v>
+        <v>0.5263296093986823</v>
       </c>
     </row>
     <row r="61">
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.9409673395990859</v>
+        <v>0.8109490328679446</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.6511378274757578</v>
+        <v>0.5263240325415316</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.634963333793937e-06</v>
+        <v>-4.817481666896968e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.9409673395990859</v>
+        <v>0.8109490328679446</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.6511322838076553</v>
+        <v>0.5263186251988746</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.9409673395990859</v>
+        <v>0.8109490328679446</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.6511273626539339</v>
+        <v>0.5263137040451532</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.9409673395990859</v>
+        <v>0.8109490328679446</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.6511274025094063</v>
+        <v>0.5263137439006255</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.9409673395990859</v>
+        <v>0.8109490328679446</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.6511273945383117</v>
+        <v>0.526313735929531</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.9409673395990859</v>
+        <v>0.8109490328679446</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.6511275539602008</v>
+        <v>0.5263138953514201</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.9409673395990859</v>
+        <v>0.8109490328679446</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.6511274583070674</v>
+        <v>0.5263137996982867</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.9409673395990859</v>
+        <v>0.8109490328679446</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.6511278090352237</v>
+        <v>0.5263141504264429</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.9409673395990859</v>
+        <v>0.8109490328679446</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.6511275619312953</v>
+        <v>0.5263139033225146</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.9409673395990859</v>
+        <v>0.8109490328679446</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.651127522075823</v>
+        <v>0.5263138634670423</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.9409673395990859</v>
+        <v>0.8109490328679446</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.6511274583070674</v>
+        <v>0.5263137996982867</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.9409673395990859</v>
+        <v>0.8109490328679446</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.6511275300469175</v>
+        <v>0.5263138714381368</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.9409673395990859</v>
+        <v>0.8109490328679446</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.6511274583070674</v>
+        <v>0.5263137996982867</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.9409673395990859</v>
+        <v>0.8109490328679446</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.6511275619312953</v>
+        <v>0.5263139033225146</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.9409673395990859</v>
+        <v>0.1662906746346532</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.651127657584429</v>
+        <v>0.5263139989756483</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.879412977671564</v>
+        <v>0.1662906746346532</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.6511275938156731</v>
+        <v>0.5263139352068924</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.9409673395990859</v>
+        <v>0.1662906746346532</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.6511275539602008</v>
+        <v>0.5263138953514201</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.9409673395990859</v>
+        <v>0.8109490328679446</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.6511275300469175</v>
+        <v>0.5263138714381368</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.540967339599086</v>
+        <v>0.8109490328679446</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.6511272829429894</v>
+        <v>0.5263136243342087</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.540967339599086</v>
+        <v>1.010949032867945</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.6511272032320445</v>
+        <v>0.5263135446232639</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.540967339599086</v>
+        <v>1.010949032867945</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.6511272510586114</v>
+        <v>0.5263135924498306</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.540967339599086</v>
+        <v>1.010949032867945</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.6511273706250283</v>
+        <v>0.5263137120162477</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.540967339599086</v>
+        <v>1.010949032867945</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.6511273546828394</v>
+        <v>0.5263136960740588</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.540967339599086</v>
+        <v>1.010949032867945</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.6511273706250283</v>
+        <v>0.5263137120162477</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.540967339599086</v>
+        <v>0.1662906746346532</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.6511273546828394</v>
+        <v>0.5263136960740588</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.4783676835986383</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.6511274104805007</v>
+        <v>0.5263137518717199</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.4783676835986383</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.6511274104805007</v>
+        <v>0.5263137518717199</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.9409673395990859</v>
+        <v>0.1662906746346532</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.6511274104805007</v>
+        <v>0.5263137518717199</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.9409673395990859</v>
+        <v>0.8109490328679446</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.6511275619312953</v>
+        <v>0.5263139033225146</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.540967339599086</v>
+        <v>0.3662906746346532</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.6511277771508458</v>
+        <v>0.5263141185420651</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.879412977671564</v>
+        <v>0.3662906746346533</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.6511276894688068</v>
+        <v>0.5263140308600261</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.9409673395990859</v>
+        <v>0.1662906746346532</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.6511276416422401</v>
+        <v>0.5263139830334594</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.9409673395990859</v>
+        <v>1.010949032867945</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.6511276894688068</v>
+        <v>0.5263140308600261</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.540967339599086</v>
+        <v>1.010949032867945</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.6511275061336341</v>
+        <v>0.5263138475248534</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.540967339599086</v>
+        <v>1.010949032867945</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.6511275141047286</v>
+        <v>0.5263138554959479</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.540967339599086</v>
+        <v>1.010949032867945</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.651127522075823</v>
+        <v>0.5263138634670423</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.540967339599086</v>
+        <v>1.010949032867945</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.6511275300469175</v>
+        <v>0.5263138714381368</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.540967339599086</v>
+        <v>1.010949032867945</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.6511275300469175</v>
+        <v>0.5263138714381368</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.540967339599086</v>
+        <v>1.010949032867945</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.6511275699023897</v>
+        <v>0.526313911293609</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.540967339599086</v>
+        <v>1.010949032867945</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.6511276336711457</v>
+        <v>0.526313975062365</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.9409673395990859</v>
+        <v>1.010949032867945</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.651127745266468</v>
+        <v>0.5263140866576873</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.9409673395990859</v>
+        <v>0.8109490328679446</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.6511277930930348</v>
+        <v>0.526314134484254</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.9409673395990859</v>
+        <v>0.8109490328679446</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.6511277532375624</v>
+        <v>0.5263140946287818</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.9409673395990859</v>
+        <v>0.8109490328679446</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.6511276814977124</v>
+        <v>0.5263140228889317</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.9409673395990859</v>
+        <v>0.8109490328679446</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.6511278010641293</v>
+        <v>0.5263141424553485</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.9409673395990859</v>
+        <v>0.8109490328679446</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.6511276416422401</v>
+        <v>0.5263139830334594</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.9409673395990859</v>
+        <v>0.8109490328679446</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.6511274104805007</v>
+        <v>0.5263137518717199</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.9409673395990859</v>
+        <v>0.8109490328679446</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.6511273626539339</v>
+        <v>0.5263137040451532</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.9409673395990859</v>
+        <v>0.8109490328679446</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.6511273945383117</v>
+        <v>0.526313735929531</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.9409673395990859</v>
+        <v>0.8109490328679446</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.6511274583070674</v>
+        <v>0.5263137996982867</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.9409673395990859</v>
+        <v>0.1662906746346532</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.6511274583070674</v>
+        <v>0.5263137996982867</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.4783676835986383</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.6511273785961228</v>
+        <v>0.5263137199873421</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.4783676835986383</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.6511272590297058</v>
+        <v>0.5263136004209251</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.9409673395990859</v>
+        <v>0.1662906746346532</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.6511272191742336</v>
+        <v>0.5263135605654528</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.9409673395990859</v>
+        <v>0.1662906746346532</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.6511273626539339</v>
+        <v>0.5263137040451532</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.4783676835986383</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.6511274981625397</v>
+        <v>0.526313839553759</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.6511274822203508</v>
+        <v>0.5263138236115701</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.6511274583070674</v>
+        <v>0.5263137996982867</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.6511274184515952</v>
+        <v>0.5263137598428144</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.4783676835986383</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.6511273148273672</v>
+        <v>0.5263136562185865</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.540967339599086</v>
+        <v>-0.4783676835986383</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.6511271952609501</v>
+        <v>0.5263135366521694</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.279412977671564</v>
+        <v>-0.2783676835986383</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.6511273148273672</v>
+        <v>0.5263136562185865</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.279412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.6511273626539339</v>
+        <v>0.5263137040451532</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.879412977671564</v>
+        <v>-1.12302604183193</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.6511274583070674</v>
+        <v>0.5263137996982867</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.879412977671564</v>
+        <v>-0.4783676835986383</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.6511273387406505</v>
+        <v>0.5263136801318699</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.540967339599086</v>
+        <v>0.04396149551800743</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.651127346711745</v>
+        <v>0.5263136881029643</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-mamba2_repeat_5_000001.xlsx
+++ b/out/LSTM-mamba2_repeat_5_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.1940155327320099</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.8109490328679446</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.1011757105588913</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.8109490328679446</v>
+        <v>-0.3700000000000002</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.01519523747265339</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.3662906746346532</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.03013186901807785</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.2783676835986383</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.0419396236538887</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.12302604183193</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.03844024986028671</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.12302604183193</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.04031132906675339</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.12302604183193</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.03877413272857666</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.12302604183193</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.0317242220044136</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.12302604183193</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.03293575346469879</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.12302604183193</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.03235005587339401</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.12302604183193</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.03279607743024826</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.12302604183193</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.02787305414676666</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.12302604183193</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.01997065916657448</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.12302604183193</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.0153999850153923</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.12302604183193</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.01609884202480316</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.12302604183193</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.02312134951353073</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.12302604183193</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.02244433760643005</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.12302604183193</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.019964799284935</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.12302604183193</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.02152715250849724</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.12302604183193</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.0227818638086319</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.12302604183193</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.02191468328237534</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.12302604183193</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.02138665318489075</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.12302604183193</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.01827201992273331</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.12302604183193</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.02203800156712532</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.12302604183193</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.02544788271188736</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.12302604183193</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.02609942108392715</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.12302604183193</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.02746476978063583</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.12302604183193</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.02390966564416885</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.12302604183193</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.01967135816812515</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.12302604183193</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.02674238383769989</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.12302604183193</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.03170847147703171</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.12302604183193</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.03298407793045044</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.12302604183193</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.03293374925851822</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.12302604183193</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.03276350349187851</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.12302604183193</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.03082934021949768</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.12302604183193</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.02759969979524612</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.12302604183193</v>
+        <v>0.16</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.02407069131731987</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.12302604183193</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.01243361458182335</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.12302604183193</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.006611596792936325</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.2783676835986383</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.006919220089912415</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.3662906746346533</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.001342818140983582</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.010949032867945</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0001825695434312802</v>
+        <v>-0.0001588062179686967</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.07860914469337262</v>
+        <v>0.06837723961618206</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.007566165179014206</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.3662906746346532</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.1574280764103516</v>
+        <v>0.1369371749774153</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3037086986530208</v>
+        <v>0.2641782655407763</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.02321376651525497</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.2783676835986383</v>
+        <v>0.3</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.6864373527319496</v>
+        <v>0.5970911109477675</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.09342198919729137</v>
+        <v>0.08126271538754888</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.03891947865486145</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.9230260418319297</v>
+        <v>-0.3</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.5691891820515259</v>
+        <v>0.4951038487907781</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.01895601654148876</v>
+        <v>0.01648880943692571</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.01462062820792198</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.4783676835986383</v>
+        <v>-0.3</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.5135324703474878</v>
+        <v>0.4466916245140131</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.0164167527850336</v>
+        <v>0.01428004178267504</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.005811654031276703</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.1662906746346532</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.5273893061463832</v>
+        <v>0.4587446700418065</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.00802490335441961</v>
+        <v>0.006979776886967036</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.02910654433071613</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.010949032867945</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.5270020424989373</v>
+        <v>0.4584071735198773</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.0038276323613109</v>
+        <v>0.003328508167813822</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.04046881198883057</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.010949032867945</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.5266232326600649</v>
+        <v>0.4580770449832429</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001591644862320643</v>
+        <v>0.001383435246383432</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.04558702558279037</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.010949032867945</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.5259744898288097</v>
+        <v>0.457512137494911</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001101576916697459</v>
+        <v>0.000957274348062574</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.03896310180425644</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.010949032867945</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.5265845531188552</v>
+        <v>0.4580422090064329</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0004569537959673552</v>
+        <v>0.0003970351027665685</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.03764832764863968</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.010949032867945</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.5263956808705008</v>
+        <v>0.4578771862965683</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002342054367763777</v>
+        <v>0.0002034695426654464</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.02574656903743744</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.010949032867945</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.5264073253788326</v>
+        <v>0.4578866712844318</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>8.895067147459162e-05</v>
+        <v>7.687879748623626e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.016126349568367</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.010949032867945</v>
+        <v>-0.16</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.5263505963279386</v>
+        <v>0.4578367140268551</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>4.653699352023e-05</v>
+        <v>3.966539438419933e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.01664039865136147</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.010949032867945</v>
+        <v>-0.3</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.5263540894113697</v>
+        <v>0.457839074699162</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>2.041022794847258e-05</v>
+        <v>1.702219755534291e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.01661932840943336</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.010949032867945</v>
+        <v>-0.3</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.5263483145940139</v>
+        <v>0.457833403190787</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>6.722163543152517e-06</v>
+        <v>5.123686696358992e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.01856490597128868</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.8109490328679446</v>
+        <v>-0.3</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.5263418525673186</v>
+        <v>0.4578271361834987</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>7.289038596293463e-08</v>
+        <v>-3.882814673064221e-07</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.01804719865322113</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.8109490328679446</v>
+        <v>-0.3</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.526335189882885</v>
+        <v>0.4578206898702409</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-2.519583929697793e-06</v>
+        <v>-2.932986608081494e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.01593013852834702</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.8109490328679446</v>
+        <v>-0.3</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5263296093986823</v>
+        <v>0.4578152061334052</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-4.04640701416283e-06</v>
+        <v>-4.36427134277522e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.01272082142531872</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.8109490328679446</v>
+        <v>-0.3</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.5263240325415316</v>
+        <v>0.457809725908838</v>
       </c>
     </row>
     <row r="62">
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.00921989418566227</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.8109490328679446</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.5263186251988746</v>
+        <v>0.457804318566181</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.009654195979237556</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.8109490328679446</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5263137040451532</v>
+        <v>0.4577993974124596</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.002845454961061478</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.8109490328679446</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5263137439006255</v>
+        <v>0.4577994372679319</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.007770538330078125</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.8109490328679446</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.526313735929531</v>
+        <v>0.4577994292968374</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.003388874232769012</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.8109490328679446</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5263138953514201</v>
+        <v>0.4577995887187266</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.01362963952124119</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.8109490328679446</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5263137996982867</v>
+        <v>0.4577994930655931</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.004301983863115311</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.8109490328679446</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5263141504264429</v>
+        <v>0.4577998437937493</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.0005584172904491425</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.8109490328679446</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5263139033225146</v>
+        <v>0.457799596689821</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.007324246689677238</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.8109490328679446</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5263138634670423</v>
+        <v>0.4577995568343487</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.01003589108586311</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.8109490328679446</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5263137996982867</v>
+        <v>0.4577994930655931</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.01105966418981552</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.8109490328679446</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5263138714381368</v>
+        <v>0.4577995648054431</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.0119971577078104</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.8109490328679446</v>
+        <v>0.16</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5263137996982867</v>
+        <v>0.4577994930655931</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.03770244121551514</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.8109490328679446</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5263139033225146</v>
+        <v>0.457799596689821</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.01183406077325344</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.1662906746346532</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5263139989756483</v>
+        <v>0.4577996923429547</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.0008288100361824036</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.1662906746346532</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5263139352068924</v>
+        <v>0.4577996285741988</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.002667725086212158</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.1662906746346532</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5263138953514201</v>
+        <v>0.4577995887187266</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.009732302278280258</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.8109490328679446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5263138714381368</v>
+        <v>0.4577995648054431</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.01118111051619053</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.8109490328679446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5263136243342087</v>
+        <v>0.4577993177015151</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.009813906624913216</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.010949032867945</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5263135446232639</v>
+        <v>0.4577992379905703</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.008595945313572884</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.010949032867945</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5263135924498306</v>
+        <v>0.457799285817137</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.003077927976846695</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.010949032867945</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5263137120162477</v>
+        <v>0.4577994053835541</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.003610566258430481</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.010949032867945</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5263136960740588</v>
+        <v>0.4577993894413652</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.001307878643274307</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.010949032867945</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5263137120162477</v>
+        <v>0.4577994053835541</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.002142999321222305</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.1662906746346532</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5263136960740588</v>
+        <v>0.4577993894413652</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-6.534159183502197e-05</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.4783676835986383</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5263137518717199</v>
+        <v>0.4577994452390263</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.003571309149265289</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.4783676835986383</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5263137518717199</v>
+        <v>0.4577994452390263</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.00967198982834816</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.1662906746346532</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5263137518717199</v>
+        <v>0.4577994452390263</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.002938210964202881</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.8109490328679446</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5263139033225146</v>
+        <v>0.457799596689821</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.008544646203517914</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.3662906746346532</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5263141185420651</v>
+        <v>0.4577998119093715</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.0004410408437252045</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.3662906746346533</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5263140308600261</v>
+        <v>0.4577997242273325</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.001485012471675873</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.1662906746346532</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5263139830334594</v>
+        <v>0.4577996764007658</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.004199586808681488</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.010949032867945</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5263140308600261</v>
+        <v>0.4577997242273325</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.005290325731039047</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.010949032867945</v>
+        <v>0.16</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5263138475248534</v>
+        <v>0.4577995408921598</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.005604062229394913</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.010949032867945</v>
+        <v>0.3</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5263138554959479</v>
+        <v>0.4577995488632542</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.009971540421247482</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.010949032867945</v>
+        <v>0.3</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5263138634670423</v>
+        <v>0.4577995568343487</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.005713682621717453</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.010949032867945</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5263138714381368</v>
+        <v>0.4577995648054431</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.004401009529829025</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.010949032867945</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5263138714381368</v>
+        <v>0.4577995648054431</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.01469116285443306</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.010949032867945</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.526313911293609</v>
+        <v>0.4577996046609155</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.01140100136399269</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.010949032867945</v>
+        <v>0.3</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.526313975062365</v>
+        <v>0.4577996684296713</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.007901202887296677</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.010949032867945</v>
+        <v>0.3</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5263140866576873</v>
+        <v>0.4577997800249937</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.001520588994026184</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.8109490328679446</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.526314134484254</v>
+        <v>0.4577998278515604</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.003309696912765503</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.8109490328679446</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5263140946287818</v>
+        <v>0.4577997879960882</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.009974170476198196</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.8109490328679446</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5263140228889317</v>
+        <v>0.4577997162562381</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.008256126195192337</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.8109490328679446</v>
+        <v>-0.3</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5263141424553485</v>
+        <v>0.4577998358226549</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.007982410490512848</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.8109490328679446</v>
+        <v>-0.16</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5263139830334594</v>
+        <v>0.4577996764007658</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.005389031022787094</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.8109490328679446</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5263137518717199</v>
+        <v>0.4577994452390263</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.005193211138248444</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.8109490328679446</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5263137040451532</v>
+        <v>0.4577993974124596</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.004361286759376526</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.8109490328679446</v>
+        <v>0.16</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.526313735929531</v>
+        <v>0.4577994292968374</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.005862805992364883</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.8109490328679446</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5263137996982867</v>
+        <v>0.4577994930655931</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.001206062734127045</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.1662906746346532</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5263137996982867</v>
+        <v>0.4577994930655931</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.0008681975305080414</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.4783676835986383</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5263137199873421</v>
+        <v>0.4577994133546485</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.001408420503139496</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.4783676835986383</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5263136004209251</v>
+        <v>0.4577992937882314</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.0004367008805274963</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.1662906746346532</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5263135605654528</v>
+        <v>0.4577992539327592</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.002137050032615662</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.1662906746346532</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5263137040451532</v>
+        <v>0.4577993974124596</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.001036517322063446</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.4783676835986383</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.526313839553759</v>
+        <v>0.4577995329210653</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.006037607789039612</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.12302604183193</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5263138236115701</v>
+        <v>0.4577995169788764</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.004828844219446182</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.12302604183193</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5263137996982867</v>
+        <v>0.4577994930655931</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.003595832735300064</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.12302604183193</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5263137598428144</v>
+        <v>0.4577994532101208</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.001205135136842728</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.4783676835986383</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5263136562185865</v>
+        <v>0.4577993495858929</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.005496319383382797</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.4783676835986383</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5263135366521694</v>
+        <v>0.4577992300194758</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.002081628888845444</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.2783676835986383</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5263136562185865</v>
+        <v>0.4577993495858929</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.0007095485925674438</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.12302604183193</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5263137040451532</v>
+        <v>0.4577993974124596</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.004643775522708893</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.12302604183193</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5263137996982867</v>
+        <v>0.4577994930655931</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.002194833010435104</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.4783676835986383</v>
+        <v>-0.1199999999999996</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5263136801318699</v>
+        <v>0.4577993734991762</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.00448303297162056</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.04396149551800743</v>
+        <v>0.02000000000000046</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5263136881029643</v>
+        <v>0.4577993814702707</v>
       </c>
     </row>
   </sheetData>
